--- a/SoData/GameData.xlsx
+++ b/SoData/GameData.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="54">
   <si>
     <t>id</t>
   </si>
@@ -126,21 +126,36 @@
     <t>res://Resource/4216_rpg_icons_16x16/rpg_icons_16x16/icons/weapons_and_clothing/wooden_shield.png</t>
   </si>
   <si>
+    <t>wooden_sword</t>
+  </si>
+  <si>
+    <t>木剑</t>
+  </si>
+  <si>
+    <t>一把基础的木剑。</t>
+  </si>
+  <si>
+    <t>res://Resource/4216_rpg_icons_16x16/rpg_icons_16x16/icons/weapons_and_clothing/sword.png</t>
+  </si>
+  <si>
+    <t>tower</t>
+  </si>
+  <si>
+    <t>哨塔</t>
+  </si>
+  <si>
+    <t>BUILDABLE</t>
+  </si>
+  <si>
+    <t>RARE</t>
+  </si>
+  <si>
+    <t>一座有攻击能力的哨塔</t>
+  </si>
+  <si>
     <t>res://Resource/Tiny Swords (Free Pack)/Buildings/Black Buildings/Tower.png</t>
   </si>
   <si>
-    <t>wooden_sword</t>
-  </si>
-  <si>
-    <t>木剑</t>
-  </si>
-  <si>
-    <t>一把基础的木剑。</t>
-  </si>
-  <si>
-    <t>res://Resource/4216_rpg_icons_16x16/rpg_icons_16x16/icons/weapons_and_clothing/sword.png</t>
-  </si>
-  <si>
     <t>result_item_id</t>
   </si>
   <si>
@@ -169,6 +184,12 @@
   </si>
   <si>
     <t>wood:4</t>
+  </si>
+  <si>
+    <t>recipe_tower</t>
+  </si>
+  <si>
+    <t>wood:4;stone:1</t>
   </si>
 </sst>
 </file>
@@ -1130,8 +1151,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="7"/>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="14.875" customWidth="1"/>
     <col min="3" max="3" width="10.375" customWidth="1"/>
@@ -1290,16 +1311,13 @@
       <c r="G6">
         <v>99</v>
       </c>
-      <c r="H6" t="s">
-        <v>32</v>
-      </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
         <v>33</v>
-      </c>
-      <c r="B7" t="s">
-        <v>34</v>
       </c>
       <c r="C7" t="s">
         <v>25</v>
@@ -1308,12 +1326,35 @@
         <v>11</v>
       </c>
       <c r="E7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" t="s">
         <v>35</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
         <v>36</v>
       </c>
-      <c r="G7">
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8">
         <v>99</v>
       </c>
     </row>
@@ -1326,11 +1367,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="4"/>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="22.625" customWidth="1"/>
     <col min="2" max="2" width="14.0833333333333" customWidth="1"/>
+    <col min="3" max="3" width="13.75" customWidth="1"/>
+    <col min="4" max="4" width="11.5" customWidth="1"/>
+    <col min="5" max="5" width="17.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1338,21 +1382,21 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
@@ -1364,12 +1408,12 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
@@ -1381,12 +1425,12 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B4" t="s">
         <v>28</v>
@@ -1398,7 +1442,24 @@
         <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>46</v>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/SoData/GameData.xlsx
+++ b/SoData/GameData.xlsx
@@ -1585,7 +1585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:L61"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1642,17 +1642,22 @@
           <t>is_material</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>socket_count</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>props</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>pack_probability</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>icon_path</t>
         </is>
@@ -1699,17 +1704,22 @@
           <t>是否可作为材料 TRUE/FALSE</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>基底可镶嵌槽位数量；非基底填 0</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>属性键值，用分号分隔，例如 森林:1;资源:2</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>卡包内抽取权重：同分类卡包内按权重随机，品质越高建议越低</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="L2" s="5" t="inlineStr">
         <is>
           <t>可选图标路径 res://...</t>
         </is>
@@ -1718,12 +1728,12 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>plain_map</t>
+          <t>forest_map</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>平原地图</t>
+          <t>森林地图</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -1738,7 +1748,7 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>基础地图基底。适合承载低风险、资源均衡的明日地图组合。</t>
+          <t>森林环境地图基底。适合生成树木、灌木、野兽和木材资源更密集的明日地图。</t>
         </is>
       </c>
       <c r="F3" s="6" t="n">
@@ -1754,29 +1764,32 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>平原:1;风险:1</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="n">
-        <v>0</v>
+      <c r="I3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>森林:2;木材:2;隐蔽:1;风险:1</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>hill</t>
+          <t>grassland_map</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>丘陵</t>
+          <t>草原地图</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>terrain</t>
+          <t>map_base</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -1786,45 +1799,48 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>提高高低差、坡地和绕路地形出现概率。</t>
+          <t>草原环境地图基底。适合生成开阔视野、低遮蔽和稳定食物来源的明日地图。</t>
         </is>
       </c>
       <c r="F4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>3</v>
       </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>高地:2;障碍:1</t>
-        </is>
-      </c>
-      <c r="J4" s="7" t="n">
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>草原:2;视野:1;风险:1</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>rock</t>
+          <t>plain_map</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>岩石</t>
+          <t>平原地图</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>terrain</t>
+          <t>map_base</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -1834,45 +1850,48 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>提高岩石地貌、碎石障碍和采石点出现概率。</t>
+          <t>基础地图基底。适合承载低风险、资源均衡的明日地图组合。</t>
         </is>
       </c>
       <c r="F5" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>岩石:1;障碍:1</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="n">
-        <v>100</v>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>平原:1;风险:1</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>cliff</t>
+          <t>ruins_map</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>断崖</t>
+          <t>遗迹地图</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>terrain</t>
+          <t>map_base</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -1882,203 +1901,215 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>提高断崖、狭窄路线和坠落风险地形出现概率。</t>
+          <t>遗迹环境地图基底。适合生成废墟建筑、容器、异常线索和更高遭遇风险。</t>
         </is>
       </c>
       <c r="F6" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>高地:2;风险:2;路线限制:1</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="n">
-        <v>35</v>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>遗迹:2;建筑:2;线索:1;风险:2</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>ash_land</t>
+          <t>snow_mountain_map</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>灰烬地</t>
+          <t>雪山地图</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>terrain</t>
+          <t>map_base</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>RARE</t>
+          <t>EPIC</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>提高烧灼地表、炭化资源和火焰风险出现概率。</t>
+          <t>雪山环境地图基底。适合生成低温、高地、视野阻碍和稀有资源。</t>
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>灰烬:2;火风险:2;炭化木:1</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="n">
-        <v>35</v>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>雪山:3;寒冷:3;高地:2;风险:3</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>meadow</t>
+          <t>swamp_map</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>草甸</t>
+          <t>沼泽地图</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>terrain</t>
+          <t>map_base</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>COMMON</t>
+          <t>RARE</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>生成开阔草甸倾向，视野更好但遮蔽物更少。</t>
+          <t>沼泽环境地图基底。适合生成水域、潮湿地形、毒性威胁和湿地资源。</t>
         </is>
       </c>
       <c r="F8" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>平原:1;草地:2;视野:1</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="n">
-        <v>100</v>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>沼泽:2;水域:2;移动惩罚:1;风险:2</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>mist_valley</t>
+          <t>volcano_map</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>雾谷</t>
+          <t>火山地图</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>terrain</t>
+          <t>map_base</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>RARE</t>
+          <t>EPIC</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>提高低能见度区域和伏击事件出现概率。</t>
+          <t>火山环境地图基底。适合生成高温、灰烬、稀有矿物和高风险路线。</t>
         </is>
       </c>
       <c r="F9" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>迷雾:2;风险:2;隐蔽:1</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="n">
-        <v>35</v>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>火山:3;火风险:3;矿物:2;风险:3</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>pond</t>
+          <t>ash_land</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>池塘</t>
+          <t>灰烬地</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>terrain</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>COMMON</t>
+          <t>RARE</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>提高池塘、水边资源和潮湿区域出现概率。</t>
+          <t>提高烧灼地表、炭化资源和火焰风险出现概率。</t>
         </is>
       </c>
       <c r="F10" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -2090,43 +2121,46 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>水域:1;食物:1</t>
-        </is>
-      </c>
-      <c r="J10" s="8" t="n">
-        <v>100</v>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>灰烬:2;火风险:2;炭化木:1</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>river</t>
+          <t>cliff</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>河流</t>
+          <t>断崖</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>terrain</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>COMMON</t>
+          <t>RARE</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>提高河道、水产和路线切割地形出现概率。</t>
+          <t>提高断崖、狭窄路线和坠落风险地形出现概率。</t>
         </is>
       </c>
       <c r="F11" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
@@ -2138,43 +2172,46 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
-        <is>
-          <t>水域:2;鱼类:1;路线限制:1</t>
-        </is>
-      </c>
-      <c r="J11" s="8" t="n">
-        <v>100</v>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>高地:2;风险:2;路线限制:1</t>
+        </is>
+      </c>
+      <c r="K11" s="8" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>swamp</t>
+          <t>hill</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>沼泽</t>
+          <t>丘陵</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>terrain</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>RARE</t>
+          <t>COMMON</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>提高泥泞湿地、减速地形和湿地资源出现概率。</t>
+          <t>提高高低差、坡地和绕路地形出现概率。</t>
         </is>
       </c>
       <c r="F12" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -2186,43 +2223,46 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>水域:2;潮湿:2;移动惩罚:1</t>
-        </is>
-      </c>
-      <c r="J12" s="8" t="n">
-        <v>35</v>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>高地:2;障碍:1</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>meadow</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>泉眼</t>
+          <t>草甸</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>terrain</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>RARE</t>
+          <t>COMMON</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>提高安全水源、恢复点和清洁资源出现概率。</t>
+          <t>生成开阔草甸倾向，视野更好但遮蔽物更少。</t>
         </is>
       </c>
       <c r="F13" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
@@ -2234,43 +2274,46 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t>水源:3;安全:1</t>
-        </is>
-      </c>
-      <c r="J13" s="8" t="n">
-        <v>35</v>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>平原:1;草地:2;视野:1</t>
+        </is>
+      </c>
+      <c r="K13" s="8" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>ancient_altar</t>
+          <t>mist_valley</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>古代祭坛</t>
+          <t>雾谷</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>terrain</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>EPIC</t>
+          <t>RARE</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>提高异常仪式、稀有事件和高代价奖励出现概率。</t>
+          <t>提高低能见度区域和伏击事件出现概率。</t>
         </is>
       </c>
       <c r="F14" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
@@ -2282,43 +2325,46 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>异常:3;奖励:3;风险:3</t>
-        </is>
-      </c>
-      <c r="J14" s="9" t="n">
-        <v>12</v>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>迷雾:2;风险:2;隐蔽:1</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>radio_tower</t>
+          <t>rock</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>广播塔</t>
+          <t>岩石</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>terrain</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>EPIC</t>
+          <t>COMMON</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>提高信号事件、线索收益和主线异常触发概率。</t>
+          <t>提高岩石地貌、碎石障碍和采石点出现概率。</t>
         </is>
       </c>
       <c r="F15" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
@@ -2330,29 +2376,32 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>信号:3;线索:2;风险:2</t>
-        </is>
-      </c>
-      <c r="J15" s="9" t="n">
-        <v>12</v>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>岩石:1;障碍:1</t>
+        </is>
+      </c>
+      <c r="K15" s="9" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>ruined_cabin</t>
+          <t>pond</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>废弃木屋</t>
+          <t>池塘</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>water</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
@@ -2362,7 +2411,7 @@
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>提高废弃建筑、容器和基础补给出现概率。</t>
+          <t>提高池塘、水边资源和潮湿区域出现概率。</t>
         </is>
       </c>
       <c r="F16" s="9" t="n">
@@ -2378,43 +2427,46 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t>建筑:1;补给:2;风险:1</t>
-        </is>
-      </c>
-      <c r="J16" s="9" t="n">
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>水域:1;食物:1</t>
+        </is>
+      </c>
+      <c r="K16" s="9" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>cave</t>
+          <t>river</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>洞穴</t>
+          <t>河流</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>water</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>RARE</t>
+          <t>COMMON</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>生成洞穴入口倾向，提高矿物和巢穴风险。</t>
+          <t>提高河道、水产和路线切割地形出现概率。</t>
         </is>
       </c>
       <c r="F17" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
@@ -2426,43 +2478,46 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>洞穴:2;矿物:1;风险:2</t>
-        </is>
-      </c>
-      <c r="J17" s="9" t="n">
-        <v>35</v>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>水域:2;鱼类:1;路线限制:1</t>
+        </is>
+      </c>
+      <c r="K17" s="9" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>bandit_camp</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>盗匪营地</t>
+          <t>泉眼</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>water</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>EPIC</t>
+          <t>RARE</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>提高人形敌人、战利品和战斗事件出现概率。</t>
+          <t>提高安全水源、恢复点和清洁资源出现概率。</t>
         </is>
       </c>
       <c r="F18" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
@@ -2474,29 +2529,32 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>营地:2;战利品:3;风险:3</t>
-        </is>
-      </c>
-      <c r="J18" s="9" t="n">
-        <v>12</v>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>水源:3;安全:1</t>
+        </is>
+      </c>
+      <c r="K18" s="9" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>mine</t>
+          <t>swamp</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>矿坑</t>
+          <t>沼泽</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>water</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
@@ -2506,7 +2564,7 @@
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>生成矿坑或地下入口倾向，提高矿物收益并增加遭遇风险。</t>
+          <t>提高泥泞湿地、减速地形和湿地资源出现概率。</t>
         </is>
       </c>
       <c r="F19" s="9" t="n">
@@ -2522,43 +2580,46 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I19" s="9" t="inlineStr">
-        <is>
-          <t>矿区:2;风险:2;矿物:2</t>
-        </is>
-      </c>
-      <c r="J19" s="9" t="n">
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>水域:2;潮湿:2;移动惩罚:1</t>
+        </is>
+      </c>
+      <c r="K19" s="9" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>dead_tree</t>
+          <t>ancient_altar</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>枯树</t>
+          <t>古代祭坛</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>plant</t>
+          <t>site</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>COMMON</t>
+          <t>EPIC</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>提高枯木、干燥地貌和可燃资源出现概率。</t>
+          <t>提高异常仪式、稀有事件和高代价奖励出现概率。</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
@@ -2570,43 +2631,46 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>枯木:2;干燥:1;火风险:1</t>
-        </is>
-      </c>
-      <c r="J20" s="6" t="n">
-        <v>100</v>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>异常:3;奖励:3;风险:3</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>tree</t>
+          <t>bandit_camp</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>树木</t>
+          <t>盗匪营地</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>plant</t>
+          <t>site</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>COMMON</t>
+          <t>EPIC</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>提高树木、林地和木材资源出现概率。</t>
+          <t>提高人形敌人、战利品和战斗事件出现概率。</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
@@ -2618,29 +2682,32 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>森林:1;木材:2</t>
-        </is>
-      </c>
-      <c r="J21" s="6" t="n">
-        <v>100</v>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>营地:2;战利品:3;风险:3</t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>hardwood</t>
+          <t>cave</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>硬木</t>
+          <t>洞穴</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>plant</t>
+          <t>site</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -2650,7 +2717,7 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>提高高品质木材和坚硬树种出现概率。</t>
+          <t>生成洞穴入口倾向，提高矿物和巢穴风险。</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
@@ -2666,43 +2733,46 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>木材:3;耐久:1</t>
-        </is>
-      </c>
-      <c r="J22" s="6" t="n">
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>洞穴:2;矿物:1;风险:2</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>mushroom</t>
+          <t>mine</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>蘑菇</t>
+          <t>矿坑</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>plant</t>
+          <t>site</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>COMMON</t>
+          <t>RARE</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>提高菌类资源和潮湿腐植环境出现概率。</t>
+          <t>生成矿坑或地下入口倾向，提高矿物收益并增加遭遇风险。</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
@@ -2714,29 +2784,32 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>菌类:1;食物:1;潮湿:1</t>
-        </is>
-      </c>
-      <c r="J23" s="6" t="n">
-        <v>100</v>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>矿区:2;风险:2;矿物:2</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>crystal</t>
+          <t>radio_tower</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>水晶簇</t>
+          <t>广播塔</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>mineral</t>
+          <t>site</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
@@ -2746,7 +2819,7 @@
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>提高异常矿物、能量反应和稀有合成材料出现概率。</t>
+          <t>提高信号事件、线索收益和主线异常触发概率。</t>
         </is>
       </c>
       <c r="F24" s="10" t="n">
@@ -2762,29 +2835,32 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
-        <is>
-          <t>水晶:3;异常:2;价值:2</t>
-        </is>
-      </c>
-      <c r="J24" s="10" t="n">
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>信号:3;线索:2;风险:2</t>
+        </is>
+      </c>
+      <c r="K24" s="10" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>coal_ore</t>
+          <t>ruined_cabin</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>煤矿</t>
+          <t>废弃木屋</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>mineral</t>
+          <t>site</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
@@ -2794,7 +2870,7 @@
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>提高煤炭、燃料和黑尘地貌出现概率。</t>
+          <t>提高废弃建筑、容器和基础补给出现概率。</t>
         </is>
       </c>
       <c r="F25" s="10" t="n">
@@ -2810,43 +2886,46 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I25" s="10" t="inlineStr">
-        <is>
-          <t>燃料:2;矿物:1</t>
-        </is>
-      </c>
-      <c r="J25" s="10" t="n">
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>建筑:1;补给:2;风险:1</t>
+        </is>
+      </c>
+      <c r="K25" s="10" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>salt</t>
+          <t>dead_tree</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>盐岩</t>
+          <t>枯树</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>mineral</t>
+          <t>plant</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>RARE</t>
+          <t>COMMON</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>提高盐岩、保存食物和干燥地貌出现概率。</t>
+          <t>提高枯木、干燥地貌和可燃资源出现概率。</t>
         </is>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
@@ -2858,43 +2937,46 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I26" s="10" t="inlineStr">
-        <is>
-          <t>盐:2;保存:1;干燥:1</t>
-        </is>
-      </c>
-      <c r="J26" s="10" t="n">
-        <v>35</v>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="10" t="inlineStr">
+        <is>
+          <t>枯木:2;干燥:1;火风险:1</t>
+        </is>
+      </c>
+      <c r="K26" s="10" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>gold_ore</t>
+          <t>hardwood</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>金矿石</t>
+          <t>硬木</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>mineral</t>
+          <t>plant</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>EPIC</t>
+          <t>RARE</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>提高高价值矿点和争夺风险。</t>
+          <t>提高高品质木材和坚硬树种出现概率。</t>
         </is>
       </c>
       <c r="F27" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
@@ -2906,29 +2988,32 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr">
-        <is>
-          <t>黄金:3;价值:3;风险:2</t>
-        </is>
-      </c>
-      <c r="J27" s="10" t="n">
-        <v>12</v>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="10" t="inlineStr">
+        <is>
+          <t>木材:3;耐久:1</t>
+        </is>
+      </c>
+      <c r="K27" s="10" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>iron_ore</t>
+          <t>mushroom</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>铁矿石</t>
+          <t>蘑菇</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>mineral</t>
+          <t>plant</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
@@ -2938,11 +3023,11 @@
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>提高铁矿节点和金属材料收益。</t>
+          <t>提高菌类资源和潮湿腐植环境出现概率。</t>
         </is>
       </c>
       <c r="F28" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
@@ -2954,29 +3039,32 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I28" s="10" t="inlineStr">
-        <is>
-          <t>铁:2;矿物:1</t>
-        </is>
-      </c>
-      <c r="J28" s="10" t="n">
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="10" t="inlineStr">
+        <is>
+          <t>菌类:1;食物:1;潮湿:1</t>
+        </is>
+      </c>
+      <c r="K28" s="10" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>copper_ore</t>
+          <t>tree</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>铜矿石</t>
+          <t>树木</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>mineral</t>
+          <t>plant</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
@@ -2986,11 +3074,11 @@
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>提高铜矿节点、线缆材料和导电异常事件概率。</t>
+          <t>提高树木、林地和木材资源出现概率。</t>
         </is>
       </c>
       <c r="F29" s="10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
@@ -3002,24 +3090,27 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I29" s="10" t="inlineStr">
-        <is>
-          <t>铜:2;导电:1</t>
-        </is>
-      </c>
-      <c r="J29" s="10" t="n">
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="10" t="inlineStr">
+        <is>
+          <t>森林:1;木材:2</t>
+        </is>
+      </c>
+      <c r="K29" s="10" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>silver_ore</t>
+          <t>clay</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>银矿石</t>
+          <t>黏土</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -3029,16 +3120,16 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>RARE</t>
+          <t>COMMON</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>提高稀有金属和高价值矿点出现概率。</t>
+          <t>提高湿润土层、陶土和建造材料出现概率。</t>
         </is>
       </c>
       <c r="F30" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
@@ -3050,24 +3141,27 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I30" s="10" t="inlineStr">
-        <is>
-          <t>银:2;价值:2;矿物:1</t>
-        </is>
-      </c>
-      <c r="J30" s="10" t="n">
-        <v>35</v>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="10" t="inlineStr">
+        <is>
+          <t>黏土:2;建材:1;潮湿:1</t>
+        </is>
+      </c>
+      <c r="K30" s="10" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>clay</t>
+          <t>coal_ore</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>黏土</t>
+          <t>煤矿</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -3082,7 +3176,7 @@
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>提高湿润土层、陶土和建造材料出现概率。</t>
+          <t>提高煤炭、燃料和黑尘地貌出现概率。</t>
         </is>
       </c>
       <c r="F31" s="10" t="n">
@@ -3098,43 +3192,46 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I31" s="10" t="inlineStr">
-        <is>
-          <t>黏土:2;建材:1;潮湿:1</t>
-        </is>
-      </c>
-      <c r="J31" s="10" t="n">
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="10" t="inlineStr">
+        <is>
+          <t>燃料:2;矿物:1</t>
+        </is>
+      </c>
+      <c r="K31" s="10" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>pumpkin</t>
+          <t>copper_ore</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>南瓜</t>
+          <t>铜矿石</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>food</t>
+          <t>mineral</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>RARE</t>
+          <t>COMMON</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>提高大型作物和高饱食度食物出现概率。</t>
+          <t>提高铜矿节点、线缆材料和导电异常事件概率。</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
@@ -3146,43 +3243,46 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>食物:3;农田:1</t>
-        </is>
-      </c>
-      <c r="J32" s="5" t="n">
-        <v>35</v>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>铜:2;导电:1</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>potato</t>
+          <t>crystal</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>土豆</t>
+          <t>水晶簇</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>food</t>
+          <t>mineral</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>COMMON</t>
+          <t>EPIC</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>提高根茎作物和耐储存食物出现概率。</t>
+          <t>提高异常矿物、能量反应和稀有合成材料出现概率。</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
@@ -3194,43 +3294,46 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>食物:2;储存:1</t>
-        </is>
-      </c>
-      <c r="J33" s="5" t="n">
-        <v>100</v>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>水晶:3;异常:2;价值:2</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>wheat</t>
+          <t>gold_ore</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>金矿石</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>food</t>
+          <t>mineral</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>COMMON</t>
+          <t>EPIC</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>提高农作物、谷物和可持续食物来源出现概率。</t>
+          <t>提高高价值矿点和争夺风险。</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
@@ -3242,29 +3345,32 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
-        <is>
-          <t>食物:2;农田:1</t>
-        </is>
-      </c>
-      <c r="J34" s="5" t="n">
-        <v>100</v>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>黄金:3;价值:3;风险:2</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>berry_bush</t>
+          <t>iron_ore</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>浆果丛</t>
+          <t>铁矿石</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>food</t>
+          <t>mineral</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -3274,11 +3380,11 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>提高浆果、灌木和低风险采集点出现概率。</t>
+          <t>提高铁矿节点和金属材料收益。</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
@@ -3290,43 +3396,46 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>食物:2;灌木:1</t>
-        </is>
-      </c>
-      <c r="J35" s="5" t="n">
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>铁:2;矿物:1</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>corn</t>
+          <t>salt</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>玉米</t>
+          <t>盐岩</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>food</t>
+          <t>mineral</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>COMMON</t>
+          <t>RARE</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>提高农田、谷物和稳定食物来源出现概率。</t>
+          <t>提高盐岩、保存食物和干燥地貌出现概率。</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
@@ -3338,43 +3447,46 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>食物:2;农田:1</t>
-        </is>
-      </c>
-      <c r="J36" s="5" t="n">
-        <v>100</v>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>盐:2;保存:1;干燥:1</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>silver_ore</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>苹果</t>
+          <t>银矿石</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>food</t>
+          <t>mineral</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>COMMON</t>
+          <t>RARE</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>提高苹果树、可食用果实和安全食物收益。</t>
+          <t>提高稀有金属和高价值矿点出现概率。</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
@@ -3386,24 +3498,27 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>食物:2;安全:1</t>
-        </is>
-      </c>
-      <c r="J37" s="5" t="n">
-        <v>100</v>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>银:2;价值:2;矿物:1</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>pineapple</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>菠萝</t>
+          <t>苹果</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -3413,16 +3528,16 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>RARE</t>
+          <t>COMMON</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>提高热带果实和高价值食物点出现概率。</t>
+          <t>提高苹果树、可食用果实和安全食物收益。</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
@@ -3434,24 +3549,27 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
-        <is>
-          <t>食物:3;热带:1</t>
-        </is>
-      </c>
-      <c r="J38" s="5" t="n">
-        <v>35</v>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>食物:2;安全:1</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>honeycomb</t>
+          <t>berry_bush</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>蜂巢</t>
+          <t>浆果丛</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -3461,16 +3579,16 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>RARE</t>
+          <t>COMMON</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>提高蜂蜜收益，同时引入蜂群威胁。</t>
+          <t>提高浆果、灌木和低风险采集点出现概率。</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
@@ -3482,24 +3600,27 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
-        <is>
-          <t>食物:2;蜂群:2;风险:1</t>
-        </is>
-      </c>
-      <c r="J39" s="5" t="n">
-        <v>35</v>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>食物:2;灌木:1</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>watermelon</t>
+          <t>corn</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>西瓜</t>
+          <t>玉米</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -3514,11 +3635,11 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>提高大型果实、水分补给和低风险食物点出现概率。</t>
+          <t>提高农田、谷物和稳定食物来源出现概率。</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
@@ -3530,43 +3651,46 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>食物:2;水分:2</t>
-        </is>
-      </c>
-      <c r="J40" s="5" t="n">
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>食物:2;农田:1</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>rabbit</t>
+          <t>honeycomb</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>兔子</t>
+          <t>蜂巢</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>creature</t>
+          <t>food</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>COMMON</t>
+          <t>RARE</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>提高小型动物、肉类和低风险狩猎点出现概率。</t>
+          <t>提高蜂蜜收益，同时引入蜂群威胁。</t>
         </is>
       </c>
       <c r="F41" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
@@ -3578,43 +3702,46 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I41" s="11" t="inlineStr">
-        <is>
-          <t>动物:1;食物:1</t>
-        </is>
-      </c>
-      <c r="J41" s="11" t="n">
-        <v>100</v>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="11" t="inlineStr">
+        <is>
+          <t>食物:2;蜂群:2;风险:1</t>
+        </is>
+      </c>
+      <c r="K41" s="11" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>bear</t>
+          <t>pineapple</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>熊</t>
+          <t>菠萝</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>creature</t>
+          <t>food</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>EPIC</t>
+          <t>RARE</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>提高大型猛兽和高价值掉落，同时显著增加战斗压力。</t>
+          <t>提高热带果实和高价值食物点出现概率。</t>
         </is>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
@@ -3626,43 +3753,46 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I42" s="11" t="inlineStr">
-        <is>
-          <t>大型野兽:3;风险:3;皮毛:2</t>
-        </is>
-      </c>
-      <c r="J42" s="11" t="n">
-        <v>12</v>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="11" t="inlineStr">
+        <is>
+          <t>食物:3;热带:1</t>
+        </is>
+      </c>
+      <c r="K42" s="11" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>fox</t>
+          <t>potato</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>狐狸</t>
+          <t>土豆</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>creature</t>
+          <t>food</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>RARE</t>
+          <t>COMMON</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>提高敏捷野兽和偷袭事件概率。</t>
+          <t>提高根茎作物和耐储存食物出现概率。</t>
         </is>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
@@ -3674,29 +3804,32 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I43" s="11" t="inlineStr">
-        <is>
-          <t>野兽:1;敏捷:2;风险:1</t>
-        </is>
-      </c>
-      <c r="J43" s="11" t="n">
-        <v>35</v>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="11" t="inlineStr">
+        <is>
+          <t>食物:2;储存:1</t>
+        </is>
+      </c>
+      <c r="K43" s="11" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>snake</t>
+          <t>pumpkin</t>
         </is>
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>蛇</t>
+          <t>南瓜</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>creature</t>
+          <t>food</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
@@ -3706,7 +3839,7 @@
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>提高毒性动物和草丛伏击概率。</t>
+          <t>提高大型作物和高饱食度食物出现概率。</t>
         </is>
       </c>
       <c r="F44" s="11" t="n">
@@ -3722,43 +3855,46 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I44" s="11" t="inlineStr">
-        <is>
-          <t>毒性:2;伏击:1;风险:2</t>
-        </is>
-      </c>
-      <c r="J44" s="11" t="n">
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="11" t="inlineStr">
+        <is>
+          <t>食物:3;农田:1</t>
+        </is>
+      </c>
+      <c r="K44" s="11" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>spider</t>
+          <t>watermelon</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>蜘蛛</t>
+          <t>西瓜</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>creature</t>
+          <t>food</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>RARE</t>
+          <t>COMMON</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>提高蛛网、毒性威胁和洞穴生态出现概率。</t>
+          <t>提高大型果实、水分补给和低风险食物点出现概率。</t>
         </is>
       </c>
       <c r="F45" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
@@ -3770,29 +3906,32 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I45" s="11" t="inlineStr">
-        <is>
-          <t>虫群:2;毒性:2;风险:2</t>
-        </is>
-      </c>
-      <c r="J45" s="11" t="n">
-        <v>35</v>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="11" t="inlineStr">
+        <is>
+          <t>食物:2;水分:2</t>
+        </is>
+      </c>
+      <c r="K45" s="11" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>bat</t>
+          <t>wheat</t>
         </is>
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>蝙蝠</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>creature</t>
+          <t>food</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
@@ -3802,11 +3941,11 @@
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>提高洞穴生物和夜间骚扰事件概率。</t>
+          <t>提高农作物、谷物和可持续食物来源出现概率。</t>
         </is>
       </c>
       <c r="F46" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
@@ -3818,24 +3957,27 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I46" s="11" t="inlineStr">
-        <is>
-          <t>洞穴:1;夜行:1;风险:1</t>
-        </is>
-      </c>
-      <c r="J46" s="11" t="n">
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="11" t="inlineStr">
+        <is>
+          <t>食物:2;农田:1</t>
+        </is>
+      </c>
+      <c r="K46" s="11" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>bison</t>
+          <t>bat</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>野牛</t>
+          <t>蝙蝠</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
@@ -3845,16 +3987,16 @@
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>EPIC</t>
+          <t>COMMON</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>提高大型兽群、肉类和皮革收益，但显著增加遭遇压力。</t>
+          <t>提高洞穴生物和夜间骚扰事件概率。</t>
         </is>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
@@ -3866,24 +4008,27 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I47" s="11" t="inlineStr">
-        <is>
-          <t>大型野兽:3;食物:3;风险:3</t>
-        </is>
-      </c>
-      <c r="J47" s="11" t="n">
-        <v>12</v>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="11" t="inlineStr">
+        <is>
+          <t>洞穴:1;夜行:1;风险:1</t>
+        </is>
+      </c>
+      <c r="K47" s="11" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>wolf</t>
+          <t>bear</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>野狼</t>
+          <t>熊</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
@@ -3893,16 +4038,16 @@
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>RARE</t>
+          <t>EPIC</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>提高狼群、追踪型敌人和皮毛掉落概率。</t>
+          <t>提高大型猛兽和高价值掉落，同时显著增加战斗压力。</t>
         </is>
       </c>
       <c r="F48" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G48" s="11" t="inlineStr">
         <is>
@@ -3914,24 +4059,27 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I48" s="11" t="inlineStr">
-        <is>
-          <t>野兽:2;风险:2;皮毛:1</t>
-        </is>
-      </c>
-      <c r="J48" s="11" t="n">
-        <v>35</v>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="11" t="inlineStr">
+        <is>
+          <t>大型野兽:3;风险:3;皮毛:2</t>
+        </is>
+      </c>
+      <c r="K48" s="11" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>boar</t>
+          <t>bison</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>野猪</t>
+          <t>野牛</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
@@ -3941,16 +4089,16 @@
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>RARE</t>
+          <t>EPIC</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>提高冲撞型野兽和肉类收益，同时增加近战风险。</t>
+          <t>提高大型兽群、肉类和皮革收益，但显著增加遭遇压力。</t>
         </is>
       </c>
       <c r="F49" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
@@ -3962,24 +4110,27 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I49" s="11" t="inlineStr">
-        <is>
-          <t>野兽:2;食物:2;风险:2</t>
-        </is>
-      </c>
-      <c r="J49" s="11" t="n">
-        <v>35</v>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="11" t="inlineStr">
+        <is>
+          <t>大型野兽:3;食物:3;风险:3</t>
+        </is>
+      </c>
+      <c r="K49" s="11" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>frog</t>
+          <t>boar</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>青蛙</t>
+          <t>野猪</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
@@ -3989,16 +4140,16 @@
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>COMMON</t>
+          <t>RARE</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>提高湿地小动物和潮湿生态出现概率。</t>
+          <t>提高冲撞型野兽和肉类收益，同时增加近战风险。</t>
         </is>
       </c>
       <c r="F50" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
@@ -4010,24 +4161,27 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I50" s="11" t="inlineStr">
-        <is>
-          <t>动物:1;潮湿:1;食物:1</t>
-        </is>
-      </c>
-      <c r="J50" s="11" t="n">
-        <v>100</v>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="11" t="inlineStr">
+        <is>
+          <t>野兽:2;食物:2;风险:2</t>
+        </is>
+      </c>
+      <c r="K50" s="11" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>deer</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>鱼群</t>
+          <t>鹿</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
@@ -4042,7 +4196,7 @@
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>提高水产食物和河流/池塘资源收益。</t>
+          <t>提高温和动物、肉类和皮革收益。</t>
         </is>
       </c>
       <c r="F51" s="11" t="n">
@@ -4058,24 +4212,27 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I51" s="11" t="inlineStr">
-        <is>
-          <t>鱼类:2;食物:1;水域:1</t>
-        </is>
-      </c>
-      <c r="J51" s="11" t="n">
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="11" t="inlineStr">
+        <is>
+          <t>动物:1;食物:2;皮革:1</t>
+        </is>
+      </c>
+      <c r="K51" s="11" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>deer</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>鹿</t>
+          <t>鱼群</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
@@ -4090,7 +4247,7 @@
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>提高温和动物、肉类和皮革收益。</t>
+          <t>提高水产食物和河流/池塘资源收益。</t>
         </is>
       </c>
       <c r="F52" s="11" t="n">
@@ -4106,29 +4263,32 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I52" s="11" t="inlineStr">
-        <is>
-          <t>动物:1;食物:2;皮革:1</t>
-        </is>
-      </c>
-      <c r="J52" s="11" t="n">
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="11" t="inlineStr">
+        <is>
+          <t>鱼类:2;食物:1;水域:1</t>
+        </is>
+      </c>
+      <c r="K52" s="11" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>storm_cloud</t>
+          <t>fox</t>
         </is>
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>暴风云</t>
+          <t>狐狸</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>hazard</t>
+          <t>creature</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
@@ -4138,7 +4298,7 @@
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>提高强风、雷雨和不稳定天气出现概率。</t>
+          <t>提高敏捷野兽和偷袭事件概率。</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
@@ -4154,43 +4314,46 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I53" s="12" t="inlineStr">
-        <is>
-          <t>天气:2;雷电:1;风险:2</t>
-        </is>
-      </c>
-      <c r="J53" s="12" t="n">
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="12" t="inlineStr">
+        <is>
+          <t>野兽:1;敏捷:2;风险:1</t>
+        </is>
+      </c>
+      <c r="K53" s="12" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>toxic_spore</t>
+          <t>frog</t>
         </is>
       </c>
       <c r="B54" s="12" t="inlineStr">
         <is>
-          <t>毒孢子</t>
+          <t>青蛙</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>hazard</t>
+          <t>creature</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>RARE</t>
+          <t>COMMON</t>
         </is>
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>提高毒雾、异常植物和持续伤害区域出现概率。</t>
+          <t>提高湿地小动物和潮湿生态出现概率。</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
@@ -4202,61 +4365,373 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I54" s="12" t="inlineStr">
-        <is>
-          <t>毒性:3;风险:2</t>
-        </is>
-      </c>
-      <c r="J54" s="12" t="n">
-        <v>35</v>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="12" t="inlineStr">
+        <is>
+          <t>动物:1;潮湿:1;食物:1</t>
+        </is>
+      </c>
+      <c r="K54" s="12" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
+          <t>rabbit</t>
+        </is>
+      </c>
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>兔子</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>creature</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>COMMON</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="inlineStr">
+        <is>
+          <t>提高小型动物、肉类和低风险狩猎点出现概率。</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G55" s="12" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H55" s="12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="12" t="inlineStr">
+        <is>
+          <t>动物:1;食物:1</t>
+        </is>
+      </c>
+      <c r="K55" s="12" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>snake</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>蛇</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>creature</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>RARE</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>提高毒性动物和草丛伏击概率。</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>2</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>毒性:2;伏击:1;风险:2</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>spider</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>蜘蛛</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>creature</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>RARE</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>提高蛛网、毒性威胁和洞穴生态出现概率。</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>2</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>虫群:2;毒性:2;风险:2</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>wolf</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>野狼</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>creature</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>RARE</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>提高狼群、追踪型敌人和皮毛掉落概率。</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>2</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>野兽:2;风险:2;皮毛:1</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>blight_core</t>
         </is>
       </c>
-      <c r="B55" s="12" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>腐化核心</t>
         </is>
       </c>
-      <c r="C55" s="12" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>hazard</t>
         </is>
       </c>
-      <c r="D55" s="12" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>EPIC</t>
         </is>
       </c>
-      <c r="E55" s="12" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>提高腐化区域、稀有材料和长期负面影响概率。</t>
         </is>
       </c>
-      <c r="F55" s="12" t="n">
+      <c r="F59" t="n">
         <v>1</v>
       </c>
-      <c r="G55" s="12" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="H55" s="12" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="I55" s="12" t="inlineStr">
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="inlineStr">
         <is>
           <t>腐化:3;异常:2;风险:3</t>
         </is>
       </c>
-      <c r="J55" s="12" t="n">
+      <c r="K59" t="n">
         <v>12</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>storm_cloud</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>暴风云</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>hazard</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>RARE</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>提高强风、雷雨和不稳定天气出现概率。</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>2</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>天气:2;雷电:1;风险:2</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>toxic_spore</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>毒孢子</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>hazard</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>RARE</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>提高毒雾、异常植物和持续伤害区域出现概率。</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>2</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>毒性:3;风险:2</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
